--- a/data/trans_dic/P64D$andando_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,68; 30,37</t>
+          <t>20,61; 29,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,49; 43,22</t>
+          <t>33,21; 43,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,28; 34,42</t>
+          <t>27,15; 34,3</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 23,77</t>
+          <t>6,75; 23,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,25; 45,76</t>
+          <t>37,32; 45,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 31,59</t>
+          <t>12,83; 31,22</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 21,6</t>
+          <t>12,17; 21,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,18; 28,15</t>
+          <t>15,61; 27,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,55; 22,49</t>
+          <t>15,66; 22,85</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,17; 29,46</t>
+          <t>21,34; 29,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,74; 40,41</t>
+          <t>20,87; 40,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,31; 32,96</t>
+          <t>22,72; 32,84</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,03; 23,09</t>
+          <t>13,01; 22,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,65; 37,39</t>
+          <t>28,98; 37,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,74; 28,52</t>
+          <t>20,19; 28,52</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68869; 101143</t>
+          <t>68657; 99352</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86439; 111537</t>
+          <t>85713; 111911</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161236; 203453</t>
+          <t>160470; 202768</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53616; 191471</t>
+          <t>54381; 191360</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>149328; 183435</t>
+          <t>149613; 183037</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155829; 381140</t>
+          <t>154747; 376675</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44481; 76910</t>
+          <t>43312; 76077</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52174; 90760</t>
+          <t>50319; 90080</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105494; 152547</t>
+          <t>106257; 155026</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99708; 138795</t>
+          <t>100520; 139329</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>99450; 193829</t>
+          <t>100089; 193361</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>212090; 313394</t>
+          <t>216012; 312164</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>256105; 453789</t>
+          <t>255714; 451392</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>418556; 546259</t>
+          <t>423386; 541374</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>676360; 977176</t>
+          <t>691675; 977130</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$andando_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,61; 29,83</t>
+          <t>20,58; 30,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,21; 43,37</t>
+          <t>32,48; 42,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,15; 34,3</t>
+          <t>27,19; 33,82</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 23,76</t>
+          <t>20,48; 28,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,32; 45,66</t>
+          <t>37,44; 46,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,83; 31,22</t>
+          <t>28,66; 34,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,17; 21,37</t>
+          <t>11,31; 19,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 27,94</t>
+          <t>22,98; 32,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,66; 22,85</t>
+          <t>17,64; 23,39</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,34; 29,58</t>
+          <t>21,41; 29,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,87; 40,32</t>
+          <t>34,36; 42,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,72; 32,84</t>
+          <t>28,88; 34,42</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,01; 22,96</t>
+          <t>20,65; 24,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,98; 37,06</t>
+          <t>34,48; 38,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,19; 28,52</t>
+          <t>27,34; 30,33</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82865</t>
+          <t>92665</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>98537</t>
+          <t>104007</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181402</t>
+          <t>196671</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68657; 99352</t>
+          <t>75497; 112228</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85713; 111911</t>
+          <t>90630; 118904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160470; 202768</t>
+          <t>175595; 218400</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>126273</t>
+          <t>152437</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>165895</t>
+          <t>186734</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292167</t>
+          <t>339171</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54381; 191360</t>
+          <t>128597; 176463</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>149613; 183037</t>
+          <t>167398; 206454</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154747; 376675</t>
+          <t>308108; 371407</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57121</t>
+          <t>63425</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73743</t>
+          <t>91558</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130864</t>
+          <t>154983</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43312; 76077</t>
+          <t>47220; 81903</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50319; 90080</t>
+          <t>77564; 108206</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106257; 155026</t>
+          <t>133198; 176661</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>117756</t>
+          <t>130799</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>159753</t>
+          <t>172630</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>277509</t>
+          <t>303429</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100520; 139329</t>
+          <t>110646; 153145</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100089; 193361</t>
+          <t>153820; 189477</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>216012; 312164</t>
+          <t>278547; 331950</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>384014</t>
+          <t>439326</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>554929</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>881942</t>
+          <t>994255</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>255714; 451392</t>
+          <t>398335; 480334</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>423386; 541374</t>
+          <t>521053; 587603</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>691675; 977130</t>
+          <t>940498; 1043525</t>
         </is>
       </c>
     </row>
